--- a/src/cassy/additional_data/templates/bolts/M12_insert.xlsx
+++ b/src/cassy/additional_data/templates/bolts/M12_insert.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\runners\bolts\geometries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laghida\Documents\Github\cassy\src\cassy\additional_data\templates\bolts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B618E19F-CF09-44E1-959B-4BEEDB31147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D68DBA0-DBEA-4DD9-8B07-87BAA96A97C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
+    <workbookView xWindow="57480" yWindow="-240" windowWidth="29040" windowHeight="15720" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
   </bookViews>
   <sheets>
     <sheet name="Insert Data" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>Dimensions of the bolts and assembled parts</t>
   </si>
@@ -151,12 +151,15 @@
   <si>
     <t>SS316L(N)-IG_SDC-IC</t>
   </si>
+  <si>
+    <t>Only parameters in blue are mandatory. If the others are not provided (i.e., left empty) they will be computed according to ISO metric.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,6 +205,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -229,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -482,11 +491,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -545,12 +606,6 @@
     <xf numFmtId="2" fontId="5" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,6 +613,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -589,8 +668,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>74351</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>113200</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>106631</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -634,7 +713,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>57375</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>124262</xdr:rowOff>
+      <xdr:rowOff>124260</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -677,8 +756,8 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>473886</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>182572</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1056,22 +1135,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53422B0-ED6B-49AF-B1B2-2F7C5139E7C1}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.53515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="44" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" style="2" customWidth="1"/>
-    <col min="4" max="11" width="11.140625" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="26.69140625" style="2" customWidth="1"/>
+    <col min="4" max="11" width="11.15234375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.84375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1080,7 +1159,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1101,7 +1180,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1201,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1143,15 +1222,15 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="18">
-        <v>30</v>
+        <v>17</v>
+      </c>
+      <c r="C5" s="19">
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>7</v>
@@ -1164,15 +1243,15 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="18">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
@@ -1185,16 +1264,14 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="19">
-        <v>29</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C7" s="29"/>
       <c r="D7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1206,16 +1283,14 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="19">
-        <v>50</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C8" s="29"/>
       <c r="D8" s="5" t="s">
         <v>7</v>
       </c>
@@ -1227,17 +1302,15 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="s">
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="16" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="1"/>
@@ -1248,17 +1321,17 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="26">
         <v>0.15</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="27" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="1"/>
@@ -1269,7 +1342,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>20</v>
       </c>
@@ -1290,7 +1363,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1303,11 +1376,13 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+    <row r="13" spans="1:11" ht="43.3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1316,7 +1391,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1329,7 +1404,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1342,7 +1417,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1356,8 +1431,9 @@
       <c r="K16" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1365,15 +1441,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100EFE0C39B20CFE747B2EDBEF1A424A9C1" ma:contentTypeVersion="14" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="fc5d43efe255f0326fdf88779d9e8cc0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71e126cb-1963-4e7b-b13a-15d2f64f78e9" xmlns:ns3="f41f4605-e15c-4135-bd96-d3970596b173" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c67b044c92a952204dd5da40bf3ff3c1" ns2:_="" ns3:_="">
     <xsd:import namespace="71e126cb-1963-4e7b-b13a-15d2f64f78e9"/>
@@ -1602,6 +1669,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1614,14 +1690,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F460EF5-1FE2-485A-B28D-6307C5242F38}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AD0DBB6-51A1-41E4-B899-7133D1D7DFCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1640,6 +1708,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F460EF5-1FE2-485A-B28D-6307C5242F38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B53875E3-DFDB-4F02-8AAC-AEAA1E089733}">
   <ds:schemaRefs>
